--- a/output/260728__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260728__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <sz val="10"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00999999"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -71,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -80,6 +85,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -476,96 +482,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] '튜더 왕조의 설계자' 토머스 크롬웰 처형 [김정한의 역사&amp;오늘]</t>
+          <t>[더팩트] 내분 '외부'로 돌리는 장동혁…'당원 권한 강화' 돌파구 될까</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/421/0009082113</t>
+          <t>https://n.news.naver.com/article/629/0000519461</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] [유효상 칼럼] 왜 국민연금은 '고래의 딜레마(The Whale's Dilemma)'에 빠졌...</t>
+          <t>[뉴스1] 李 대통령이 띄운 임신중지약…하반기 복지위 '뜨거운 감자'</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/008/0005391781</t>
+          <t>https://n.news.naver.com/article/421/0009082119</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[세계일보] 성남시장 “정부 부동산 정책은 ‘규제 일변도’”</t>
+          <t>[서울신문] 민주 “혈세 397억 반드시 회수”… 국힘 “434억 걸린 李 재판 재개”</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/022/0004146385</t>
+          <t>https://n.news.naver.com/article/081/0003665127</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[데일리안] 베를린 퀴어축제 테러 충격…독일 극우당 '반사이익’</t>
+          <t>[동아일보] 경남 진주 ‘발전공기업 통합 본사’ 유치전 참전</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/119/0003115471</t>
+          <t>https://n.news.naver.com/article/020/0003736917</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[뉴시스] "자유는 공짜 아냐" 6·25 정전 73주년에 美 추모행렬</t>
+          <t>[한국일보] 與 '필리버스터·패스트트랙' 개정 착수… "다수당 독주, 헌법 정신 훼손...</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/003/0014091642</t>
+          <t>https://n.news.naver.com/article/469/0000944718</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[서울경제] 트럼프 “美, 금리 내리면 12% 성장 가능...워시는 훌륭한데 이사들이 정...</t>
+          <t>[동아일보] 충남 여야의원 “발전통합본사 유치” 촉구</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/011/0004645793</t>
+          <t>https://n.news.naver.com/article/020/0003736895</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] [세종로의 아침] ‘바퀴벌레’의 힘</t>
+          <t>[YTN] "이번 주 처리" 속도전에 국힘 격앙...또 필버 정국?</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/081/0003665199</t>
+          <t>https://n.news.naver.com/article/052/0002385357</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] ‘IS 추종’ 독일 테러 용의자 사살… “극단주의 경계”</t>
+          <t>[SBS] "새 술은 새 부대에" 또 사의…청와대는 "사실 아냐"</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/081/0003665141</t>
+          <t>https://n.news.naver.com/article/055/0001375816</t>
         </is>
       </c>
     </row>
@@ -577,196 +583,90 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>[조선일보] 패싸움 양상으로 가는 ‘팀 김민석’ vs ‘팀 정청래’</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/023/0003989959</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>[더팩트] '일반 선거인의 인상' 윤석열 유죄 결정적…이재명 판결도 관통</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/629/0000519455</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>[더팩트] 내분 '외부'로 돌리는 장동혁…'당원 권한 강화' 돌파구 될까</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/629/0000519461</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>3) 국민의힘 동정</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>[중앙일보] 정청래 “조국혁신당과 통합했어야…합당했다면 서울시장 이겼을 것”</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/025/0003540488</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>[뉴시스] 정청래 "조국혁신당과 합당했다면 서울시장 이겼을 것"</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/003/0014091416</t>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>(해당 시간대 기사 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>4) 경제 동정</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>3) 국민의힘 동정</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>[뉴시스] "믿을 건 실적 뿐"…역대급 성적표로 반등 모멘텀 잡을까</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>https://n.news.naver.com/article/003/0014091671</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] ‘장외 정치’ 이어 ‘선거소청 정치’ 나선 장동혁</t>
+          <t>[데일리안] AI 투자 늘린 빅테크, 주가는 급락…"시장이 장기 가치를 과소평가"</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/020/0003736939</t>
+          <t>https://n.news.naver.com/article/119/0003115472</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] [사진] 국힘 시한폭탄 권영진, 정점식에 ‘멱살’ 사과</t>
+          <t>[서울경제] 사우디 핵협상 뒤엔 트럼프 가족?…NYT “트럼프, 원전에 이해충돌 논란...</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/025/0003540553</t>
+          <t>https://n.news.naver.com/article/011/0004645802</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 李 대통령이 띄운 임신중지약…하반기 복지위 '뜨거운 감자'</t>
+          <t>[뉴스1] 엔비디아 5% 급락…'순환금융' 우려에 SK하닉 ADR 7% 넘게 후퇴</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/421/0009082119</t>
+          <t>https://n.news.naver.com/article/421/0009082077</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] [단독] 빚 연체기록 전부 지워줬더니…6명 중 1명 올해 또 연체했다</t>
+          <t>[서울신문] 한화오션 2분기 영업익 7361억… 98% 뛰어 분기 ‘최대 실적’</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/025/0003540584</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>[이데일리] 괴롭힘 신고해도 64%는 '주의'로 끝…피해자만 웁니다</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/018/0006337863</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>4) 경제 동정</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>[한겨레] [단독] “6살 소녀 파괴한 SNS ‘설계된 중독’ 입증…메타·구글에 승소...</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/028/0002816003</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>[동아일보] [단독]“두더지 심기보다 사람 빼가기… 1명 가면 기업비밀 다 따라가”</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/020/0003736966</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>[동아일보] [단독]배터리 인재를 건설사에 고용, ‘커리어 세탁’ 뒤 기술 빼가</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/020/0003736970</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>[이데일리] [속보]李대통령 “브라질과 방산·항공우주·핵심 광물·디지털경제미래...</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/018/0006337832</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>[MBC] 소비자 심리 3개월 연속 개선‥"반도체 수출 호조·임금 상승 기대"</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>https://n.news.naver.com/article/214/0001514242</t>
+          <t>https://n.news.naver.com/article/081/0003665183</t>
         </is>
       </c>
     </row>

--- a/output/260728__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260728__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -482,96 +482,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[더팩트] 내분 '외부'로 돌리는 장동혁…'당원 권한 강화' 돌파구 될까</t>
+          <t>[중앙일보] 김부선 “주저없이 ‘알정찍’”∙∙∙정청래 공개 지지 나섰다</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/629/0000519461</t>
+          <t>https://www.joongang.co.kr/article/25448760?utm_source=navernewsstand&amp;utm_medium=referral&amp;utm_campaign=leftbottom4_newsstand&amp;utm_content=260728</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[뉴스1] 李 대통령이 띄운 임신중지약…하반기 복지위 '뜨거운 감자'</t>
+          <t>[동아일보] 장동혁 “부동산 지옥에 사는 국민, 이 정권 지옥으로 보낼 것”</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/421/0009082119</t>
+          <t>https://www.donga.com/news/NewsStand/article/all/20260728/134379395/1?utm_source=newsstand&amp;utm_medium=referral&amp;utm_campaign=main3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 민주 “혈세 397억 반드시 회수”… 국힘 “434억 걸린 李 재판 재개”</t>
+          <t>[한겨레] 장동혁 “임기 연장 개헌 시도 땐 남은 임기 못 채울 것”</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/081/0003665127</t>
+          <t>https://www.hani.co.kr/arti/politics/politics_general/1270320.html?utm_source=naver&amp;utm_medium=referral&amp;utm_campaign=newsstand&amp;utm_term=t2&amp;utm_content=20260728</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 경남 진주 ‘발전공기업 통합 본사’ 유치전 참전</t>
+          <t>[국민일보] 정점식 “권영진 선처 바라” 했지만…”책임 물어야” 쪼개진 국힘</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/020/0003736917</t>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=9000000103&amp;code=61111111&amp;sid1=pol&amp;cp=nv2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[한국일보] 與 '필리버스터·패스트트랙' 개정 착수… "다수당 독주, 헌법 정신 훼손...</t>
+          <t>[국민일보] 한동훈, ‘보완수사 폐지’ 반대 필리버스터 검토…국힘 공조 이뤄질까</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/469/0000944718</t>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=9000000107&amp;code=61111111&amp;sid1=pol&amp;cp=nv2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 충남 여야의원 “발전통합본사 유치” 촉구</t>
+          <t>[서울신문] 홍준표 “윤석열·한동훈 데려와 보수 망친 자들, 이제 책임져라”</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/020/0003736895</t>
+          <t>https://www.seoul.co.kr/news/politics/2026/07/28/20260728500197?wlog_sub=svt_006</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[YTN] "이번 주 처리" 속도전에 국힘 격앙...또 필버 정국?</t>
+          <t>[서울신문] 정청래, 충청권 투표 첫날 세종行…“이해찬 정신 계승할 것”</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/052/0002385357</t>
+          <t>https://www.seoul.co.kr/news/politics/2026/07/28/20260728500123?wlog_sub=svt_006</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[SBS] "새 술은 새 부대에" 또 사의…청와대는 "사실 아냐"</t>
+          <t>[MBC] 김민석 "근거 없이 대통령 비난하면, 짚을 건 짚겠다"</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://n.news.naver.com/article/055/0001375816</t>
+          <t>https://imnews.imbc.com/news/2026/politics/article/6840617_36911.html</t>
         </is>
       </c>
     </row>

--- a/output/260728__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260728__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -482,96 +482,96 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>[중앙일보] 김부선 “주저없이 ‘알정찍’”∙∙∙정청래 공개 지지 나섰다</t>
+          <t>[동아일보] 조정식 “현직 대통령 연임, 국민 선택 문제…내년이 개헌 적기”</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>https://www.joongang.co.kr/article/25448760?utm_source=navernewsstand&amp;utm_medium=referral&amp;utm_campaign=leftbottom4_newsstand&amp;utm_content=260728</t>
+          <t>https://www.donga.com/news/NewsStand/article/all/20260728/134378282/1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 장동혁 “부동산 지옥에 사는 국민, 이 정권 지옥으로 보낼 것”</t>
+          <t>[서울신문] 통영시장 선거 재검표 ‘표차 44→38표’…강석주 당선 유지</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>https://www.donga.com/news/NewsStand/article/all/20260728/134379395/1?utm_source=newsstand&amp;utm_medium=referral&amp;utm_campaign=main3</t>
+          <t>https://www.seoul.co.kr/news/politics/2026/07/28/20260728500009</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[한겨레] 장동혁 “임기 연장 개헌 시도 땐 남은 임기 못 채울 것”</t>
+          <t>[서울신문] 경찰, 아동 성매매 혐의 최영중 전 청주시의원 구속영장</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://www.hani.co.kr/arti/politics/politics_general/1270320.html?utm_source=naver&amp;utm_medium=referral&amp;utm_campaign=newsstand&amp;utm_term=t2&amp;utm_content=20260728</t>
+          <t>https://www.seoul.co.kr/news/society/2026/07/28/20260728500157</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] 정점식 “권영진 선처 바라” 했지만…”책임 물어야” 쪼개진 국힘</t>
+          <t>[동아일보] 與 전대 첫날 온라인 투표 먹통…“충북 권리당원 참여 차질”</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://www.kmib.co.kr/article/view.asp?arcid=9000000103&amp;code=61111111&amp;sid1=pol&amp;cp=nv2</t>
+          <t>https://www.donga.com/news/NewsStand/article/all/20260728/134377773/2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] 한동훈, ‘보완수사 폐지’ 반대 필리버스터 검토…국힘 공조 이뤄질까</t>
+          <t>[국민일보] [단독] “檢, 수사 못하는데 파견검사는 가능한가” 선관위 특검 난맥상</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://www.kmib.co.kr/article/view.asp?arcid=9000000107&amp;code=61111111&amp;sid1=pol&amp;cp=nv2</t>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=0030172407&amp;code=61111111&amp;sid1=pol</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 홍준표 “윤석열·한동훈 데려와 보수 망친 자들, 이제 책임져라”</t>
+          <t>[문화일보] 4개월 전 ‘신천지, 민주당도 가입’ 진술 확보했지만…밍기적 합수본</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://www.seoul.co.kr/news/politics/2026/07/28/20260728500197?wlog_sub=svt_006</t>
+          <t>https://www.munhwa.com/article/11605394</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 정청래, 충청권 투표 첫날 세종行…“이해찬 정신 계승할 것”</t>
+          <t>[머니투데이] "영원한 우정" 李대통령, 룰라 만나고 상파울루行…양국 기업인 '총출동'</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://www.seoul.co.kr/news/politics/2026/07/28/20260728500123?wlog_sub=svt_006</t>
+          <t>https://www.mt.co.kr/politics/2026/07/28/2026072813283328554?STAND=MT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[MBC] 김민석 "근거 없이 대통령 비난하면, 짚을 건 짚겠다"</t>
+          <t>[경향신문] 사설 윤석열 선거법 징역형, 대선 후보의 거짓말 엄중 단죄 마땅하다</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://imnews.imbc.com/news/2026/politics/article/6840617_36911.html</t>
+          <t>https://www.khan.co.kr/article/202607271810001/?nv=stand</t>
         </is>
       </c>
     </row>

--- a/output/260728__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260728__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -506,72 +506,72 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>[서울신문] 경찰, 아동 성매매 혐의 최영중 전 청주시의원 구속영장</t>
+          <t>[동아일보] 與 전대 첫날 온라인 투표 먹통…“충북 권리당원 참여 차질”</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://www.seoul.co.kr/news/society/2026/07/28/20260728500157</t>
+          <t>https://www.donga.com/news/NewsStand/article/all/20260728/134377773/2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[동아일보] 與 전대 첫날 온라인 투표 먹통…“충북 권리당원 참여 차질”</t>
+          <t>[국민일보] [단독] “檢, 수사 못하는데 파견검사는 가능한가” 선관위 특검 난맥상</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://www.donga.com/news/NewsStand/article/all/20260728/134377773/2</t>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=0030172407&amp;code=61111111&amp;sid1=pol</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] [단독] “檢, 수사 못하는데 파견검사는 가능한가” 선관위 특검 난맥상</t>
+          <t>[문화일보] 4개월 전 ‘신천지, 민주당도 가입’ 진술 확보했지만…밍기적 합수본</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://www.kmib.co.kr/article/view.asp?arcid=0030172407&amp;code=61111111&amp;sid1=pol</t>
+          <t>https://www.munhwa.com/article/11605394</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>[문화일보] 4개월 전 ‘신천지, 민주당도 가입’ 진술 확보했지만…밍기적 합수본</t>
+          <t>[머니투데이] "영원한 우정" 李대통령, 룰라 만나고 상파울루行…양국 기업인 '총출동'</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://www.munhwa.com/article/11605394</t>
+          <t>https://www.mt.co.kr/politics/2026/07/28/2026072813283328554?STAND=MT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>[머니투데이] "영원한 우정" 李대통령, 룰라 만나고 상파울루行…양국 기업인 '총출동'</t>
+          <t>[문화일보] “국회로 돌아가겠다, 당장”… 정성호, 이미 세달 전 사의 표명했다</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>https://www.mt.co.kr/politics/2026/07/28/2026072813283328554?STAND=MT</t>
+          <t>https://www.munhwa.com/article/11605444</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>[경향신문] 사설 윤석열 선거법 징역형, 대선 후보의 거짓말 엄중 단죄 마땅하다</t>
+          <t>[중앙일보] 김부선 “주저없이 ‘알정찍’”∙∙∙정청래 공개 지지 나섰다</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>https://www.khan.co.kr/article/202607271810001/?nv=stand</t>
+          <t>https://www.joongang.co.kr/article/25448760</t>
         </is>
       </c>
     </row>

--- a/output/260728__일일_정치_정당_경제_주요_기사_정리.xlsx
+++ b/output/260728__일일_정치_정당_경제_주요_기사_정리.xlsx
@@ -518,24 +518,24 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>[국민일보] [단독] “檢, 수사 못하는데 파견검사는 가능한가” 선관위 특검 난맥상</t>
+          <t>[문화일보] 4개월 전 ‘신천지, 민주당도 가입’ 진술 확보했지만…밍기적 합수본</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>https://www.kmib.co.kr/article/view.asp?arcid=0030172407&amp;code=61111111&amp;sid1=pol</t>
+          <t>https://www.munhwa.com/article/11605394</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>[문화일보] 4개월 전 ‘신천지, 민주당도 가입’ 진술 확보했지만…밍기적 합수본</t>
+          <t>[국민일보] [단독] “檢, 수사 못하는데 파견검사는 가능한가” 선관위 특검 난맥상</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>https://www.munhwa.com/article/11605394</t>
+          <t>https://www.kmib.co.kr/article/view.asp?arcid=0030172407&amp;code=61111111&amp;sid1=pol</t>
         </is>
       </c>
     </row>
